--- a/Files/2-nd course/4-th semester/Probability theory/Laboratory work/Lab #1/Vlad/Теорвер.xlsx
+++ b/Files/2-nd course/4-th semester/Probability theory/Laboratory work/Lab #1/Vlad/Теорвер.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Владислав\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Codespace\Files\2-nd course\4-th semester\Probability theory\Laboratory work\Lab #1\Vlad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26C4B79-67F3-406E-8BD8-6B8FBF32BF4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318F2AC4-7C26-450F-8AA8-C2AD5458EF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="348" windowWidth="30936" windowHeight="17040" xr2:uid="{238F68E3-D8EC-4A8A-AD0E-854BE4B44AFF}"/>
+    <workbookView xWindow="38280" yWindow="5640" windowWidth="25425" windowHeight="16440" activeTab="1" xr2:uid="{238F68E3-D8EC-4A8A-AD0E-854BE4B44AFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Выборки" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>X</t>
   </si>
@@ -74,6 +74,15 @@
   </si>
   <si>
     <t>коэф вари</t>
+  </si>
+  <si>
+    <t>эксцесс</t>
+  </si>
+  <si>
+    <t>корелл</t>
+  </si>
+  <si>
+    <t>ассим</t>
   </si>
 </sst>
 </file>
@@ -15737,6 +15746,9 @@
       <c r="A9" s="4">
         <v>6</v>
       </c>
+      <c r="D9" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="G9" s="4">
         <v>23</v>
       </c>
@@ -16959,13 +16971,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11493C69-34E8-4651-96D0-E0FD1D78BE5D}">
-  <dimension ref="A2:D61"/>
+  <dimension ref="A2:F61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="18"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="18">
         <v>8.3000000000000007</v>
       </c>
@@ -16976,8 +16988,11 @@
         <f>CORREL(A2:A61,B2:B61)</f>
         <v>0.49699651004873413</v>
       </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="18">
         <v>9.8000000000000007</v>
       </c>
@@ -16985,23 +17000,45 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="18">
         <v>6.2</v>
       </c>
       <c r="B4" s="18">
         <v>23</v>
       </c>
+      <c r="D4">
+        <f>KURT(A2:A61)</f>
+        <v>-0.98387904749708577</v>
+      </c>
+      <c r="E4">
+        <f>KURT(B2:B61)</f>
+        <v>-0.16448182227108488</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="18">
         <v>8.1999999999999993</v>
       </c>
       <c r="B5" s="18">
         <v>44</v>
       </c>
+      <c r="D5">
+        <f>SKEW(A2:A61)</f>
+        <v>-0.32741640519979015</v>
+      </c>
+      <c r="E5">
+        <f>SKEW(B2:B61)</f>
+        <v>0.2214523374831695</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="18">
         <v>8.4</v>
       </c>
@@ -17009,7 +17046,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="18">
         <v>9.1999999999999993</v>
       </c>
@@ -17017,7 +17054,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="18">
         <v>5.7</v>
       </c>
@@ -17025,7 +17062,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="18">
         <v>9</v>
       </c>
@@ -17033,7 +17070,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="18">
         <v>8.1999999999999993</v>
       </c>
@@ -17041,7 +17078,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="18">
         <v>6.9</v>
       </c>
@@ -17049,7 +17086,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="18">
         <v>8.9</v>
       </c>
@@ -17057,7 +17094,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="18">
         <v>8.6</v>
       </c>
@@ -17065,7 +17102,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="18">
         <v>7.1</v>
       </c>
@@ -17073,7 +17110,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="18">
         <v>9.1</v>
       </c>
@@ -17081,7 +17118,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="18">
         <v>9.3000000000000007</v>
       </c>
